--- a/tests/workbooktests/workbooks/test_grid.xlsx
+++ b/tests/workbooktests/workbooks/test_grid.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{20CAF07B-325F-4229-85B9-119A2F6BA981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28526D5-6D9A-448A-8D9E-24B1E100640D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6630" yWindow="-20745" windowWidth="21330" windowHeight="15900" xr2:uid="{B6BD0135-4E25-414B-A5E1-D18D565B283E}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{B6BD0135-4E25-414B-A5E1-D18D565B283E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -497,7 +497,7 @@
       </c>
       <c r="B9" t="str" cm="1">
         <f t="array" ref="B9">_xll.qlTimeGrid(B2,B3)</f>
-        <v>⚡[Book1]Sheet1!R9C2TimeGrid,A</v>
+        <v>欣[test_grid.xlsx]Sheet1!R9C2TimeGrid,A</v>
       </c>
       <c r="C9" cm="1">
         <f t="array" ref="C9:H9">TRANSPOSE(_xll.qlTimeGridTimes(B9))</f>
@@ -525,7 +525,7 @@
       </c>
       <c r="B10" t="str" cm="1">
         <f t="array" ref="B10">_xll.qlTimeGridFromTimes(B5:B7)</f>
-        <v>⚡[Book1]Sheet1!R10C2TimeGrid,A</v>
+        <v>欣[test_grid.xlsx]Sheet1!R10C2TimeGrid,A</v>
       </c>
       <c r="C10" cm="1">
         <f t="array" ref="C10:F10">TRANSPOSE(_xll.qlTimeGridTimes(B10))</f>
@@ -547,7 +547,7 @@
       </c>
       <c r="B11" t="str" cm="1">
         <f t="array" ref="B11">_xll.qlTimeGridWithMandatoryTimes(B5:B7,B3)</f>
-        <v>⚡[Book1]Sheet1!R11C2TimeGrid,A</v>
+        <v>欣[test_grid.xlsx]Sheet1!R11C2TimeGrid,A</v>
       </c>
       <c r="C11" cm="1">
         <f t="array" ref="C11:H11">TRANSPOSE(_xll.qlTimeGridTimes(B11))</f>
